--- a/api_football/League_Starts_updated.xlsx
+++ b/api_football/League_Starts_updated.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greg\Matchday Insights\api_football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5327A14B-6706-4AAA-BAD9-AEAE0E2ACA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313DDAD2-D93E-4F49-B57B-3739033F37C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1916,7 +1915,7 @@
         <v>83</v>
       </c>
       <c r="C82">
-        <v>1211.9098072174229</v>
+        <v>1211.9098072174233</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -1924,7 +1923,7 @@
         <v>84</v>
       </c>
       <c r="C83">
-        <v>1204.8808458897549</v>
+        <v>1204.8808458897552</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -1932,7 +1931,7 @@
         <v>85</v>
       </c>
       <c r="C84">
-        <v>1182.805019437224</v>
+        <v>1182.8050194372245</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -1948,7 +1947,7 @@
         <v>87</v>
       </c>
       <c r="C86">
-        <v>1109.553660967988</v>
+        <v>1109.5536609679884</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
@@ -1956,7 +1955,7 @@
         <v>88</v>
       </c>
       <c r="C87">
-        <v>1094.543584009331</v>
+        <v>1094.5435840093307</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -1972,7 +1971,7 @@
         <v>90</v>
       </c>
       <c r="C89">
-        <v>985.1493730154649</v>
+        <v>972.17112470004713</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
@@ -1980,7 +1979,7 @@
         <v>91</v>
       </c>
       <c r="C90">
-        <v>985.04449803642012</v>
+        <v>967.45946634426366</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -1996,7 +1995,7 @@
         <v>93</v>
       </c>
       <c r="C92">
-        <v>960.83353304355501</v>
+        <v>957.33731367789301</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
@@ -2004,7 +2003,7 @@
         <v>94</v>
       </c>
       <c r="C93">
-        <v>959.19859747467785</v>
+        <v>954.11070306209308</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -2012,7 +2011,7 @@
         <v>95</v>
       </c>
       <c r="C94">
-        <v>957.24932764425705</v>
+        <v>943.07180297219907</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
@@ -2020,7 +2019,7 @@
         <v>96</v>
       </c>
       <c r="C95">
-        <v>944.64037604984765</v>
+        <v>909.58235861575417</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
@@ -2028,103 +2027,103 @@
         <v>97</v>
       </c>
       <c r="C96">
-        <v>909.36135294100143</v>
+        <v>908.55315938451929</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C97">
-        <v>907.9044240064793</v>
+        <v>905.08799191570836</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C98">
-        <v>906.96994291789395</v>
+        <v>877.51140577273907</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C99">
-        <v>906.48396260417746</v>
+        <v>857.70560111730811</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C100">
-        <v>895.89693196294729</v>
+        <v>856.1565949216556</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C101">
-        <v>861.1311740544453</v>
+        <v>855.97556275080058</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C102">
-        <v>860.60584937719364</v>
+        <v>852.3261456691057</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C103">
-        <v>859.11127715079192</v>
+        <v>848.61729643255376</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C104">
-        <v>858.97468681209011</v>
+        <v>843.53262162350927</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C105">
-        <v>858.56665841193831</v>
+        <v>820.42895916424345</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C106">
-        <v>857.01615163032591</v>
+        <v>819.12907082350705</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107">
-        <v>856.30670058368457</v>
+        <v>814.00777279263048</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108">
-        <v>851.9284078147964</v>
+        <v>805.24193211912291</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
@@ -2132,7 +2131,7 @@
         <v>110</v>
       </c>
       <c r="C109">
-        <v>850.60714045340922</v>
+        <v>795.15290571719936</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
@@ -2140,31 +2139,31 @@
         <v>111</v>
       </c>
       <c r="C110">
-        <v>844.19228728892267</v>
+        <v>794.67167550776446</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C111">
-        <v>820.65520555266278</v>
+        <v>790.00713698612094</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C112">
-        <v>808.25231487301005</v>
+        <v>789.99362238663866</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C113">
-        <v>793.22798487945977</v>
+        <v>721.92770848403484</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -2172,31 +2171,31 @@
         <v>115</v>
       </c>
       <c r="C114">
-        <v>790.33200920705144</v>
+        <v>721.6188793057969</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C115">
-        <v>790.06847451714793</v>
+        <v>721.19489348482614</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C116">
-        <v>722.66052348324365</v>
+        <v>713.68353974293655</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C117">
-        <v>721.92770848403484</v>
+        <v>713.62247182633575</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -2204,7 +2203,7 @@
         <v>119</v>
       </c>
       <c r="C118">
-        <v>720.46207848561733</v>
+        <v>713.50033599313429</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -2236,7 +2235,7 @@
         <v>123</v>
       </c>
       <c r="C122">
-        <v>696.73910558891532</v>
+        <v>694.28995056875033</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">

--- a/api_football/League_Starts_updated.xlsx
+++ b/api_football/League_Starts_updated.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greg\Matchday Insights\api_football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313DDAD2-D93E-4F49-B57B-3739033F37C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681AF3FF-07ED-4B96-B370-DD9538A79814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029" calcMode="manual" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1923,7 +1923,7 @@
         <v>84</v>
       </c>
       <c r="C83">
-        <v>1204.8808458897552</v>
+        <v>1203.4724433501649</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -1931,7 +1931,7 @@
         <v>85</v>
       </c>
       <c r="C84">
-        <v>1182.8050194372245</v>
+        <v>1162.3197314317185</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -1939,7 +1939,7 @@
         <v>86</v>
       </c>
       <c r="C85">
-        <v>1127.12089187796</v>
+        <v>1111.4325795459979</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -1947,7 +1947,7 @@
         <v>87</v>
       </c>
       <c r="C86">
-        <v>1109.5536609679884</v>
+        <v>1064.8333591802541</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
@@ -1955,7 +1955,7 @@
         <v>88</v>
       </c>
       <c r="C87">
-        <v>1094.5435840093307</v>
+        <v>1063.7567329373524</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -1963,7 +1963,7 @@
         <v>89</v>
       </c>
       <c r="C88">
-        <v>1062.165014331219</v>
+        <v>971.12173219213901</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
@@ -1971,7 +1971,7 @@
         <v>90</v>
       </c>
       <c r="C89">
-        <v>972.17112470004713</v>
+        <v>963.71235936243943</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
@@ -1979,7 +1979,7 @@
         <v>91</v>
       </c>
       <c r="C90">
-        <v>967.45946634426366</v>
+        <v>960.33200543055341</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -1987,7 +1987,7 @@
         <v>92</v>
       </c>
       <c r="C91">
-        <v>961.07309939482468</v>
+        <v>957.60057630407732</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
@@ -1995,7 +1995,7 @@
         <v>93</v>
       </c>
       <c r="C92">
-        <v>957.33731367789301</v>
+        <v>874.19803720558264</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
@@ -2003,7 +2003,7 @@
         <v>94</v>
       </c>
       <c r="C93">
-        <v>954.11070306209308</v>
+        <v>899.64924065505113</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -2011,7 +2011,7 @@
         <v>95</v>
       </c>
       <c r="C94">
-        <v>943.07180297219907</v>
+        <v>881.94004654856303</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
@@ -2019,7 +2019,7 @@
         <v>96</v>
       </c>
       <c r="C95">
-        <v>909.58235861575417</v>
+        <v>863.75012669651005</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
@@ -2027,7 +2027,7 @@
         <v>97</v>
       </c>
       <c r="C96">
-        <v>908.55315938451929</v>
+        <v>859.39041226328425</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
@@ -2035,7 +2035,7 @@
         <v>100</v>
       </c>
       <c r="C97">
-        <v>905.08799191570836</v>
+        <v>858.69138416448686</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
@@ -2043,7 +2043,7 @@
         <v>98</v>
       </c>
       <c r="C98">
-        <v>877.51140577273907</v>
+        <v>849.57181087023196</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
@@ -2051,7 +2051,7 @@
         <v>102</v>
       </c>
       <c r="C99">
-        <v>857.70560111730811</v>
+        <v>841.06854287668136</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
@@ -2059,7 +2059,7 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>856.1565949216556</v>
+        <v>835.87748172126305</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
@@ -2067,7 +2067,7 @@
         <v>101</v>
       </c>
       <c r="C101">
-        <v>855.97556275080058</v>
+        <v>827.54911534074768</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
@@ -2075,7 +2075,7 @@
         <v>106</v>
       </c>
       <c r="C102">
-        <v>852.3261456691057</v>
+        <v>819.87881787787353</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
@@ -2083,7 +2083,7 @@
         <v>105</v>
       </c>
       <c r="C103">
-        <v>848.61729643255376</v>
+        <v>805.19816215656249</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
@@ -2091,7 +2091,7 @@
         <v>109</v>
       </c>
       <c r="C104">
-        <v>843.53262162350927</v>
+        <v>797.73307817732814</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
@@ -2099,7 +2099,7 @@
         <v>103</v>
       </c>
       <c r="C105">
-        <v>820.42895916424345</v>
+        <v>793.1506992041883</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
@@ -2107,7 +2107,7 @@
         <v>104</v>
       </c>
       <c r="C106">
-        <v>819.12907082350705</v>
+        <v>791.0196221325283</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
@@ -2115,7 +2115,7 @@
         <v>107</v>
       </c>
       <c r="C107">
-        <v>814.00777279263048</v>
+        <v>790.77389069675439</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
@@ -2123,7 +2123,7 @@
         <v>108</v>
       </c>
       <c r="C108">
-        <v>805.24193211912291</v>
+        <v>790.08474558520413</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
@@ -2131,7 +2131,7 @@
         <v>110</v>
       </c>
       <c r="C109">
-        <v>795.15290571719936</v>
+        <v>790.0581873513903</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
@@ -2139,7 +2139,7 @@
         <v>111</v>
       </c>
       <c r="C110">
-        <v>794.67167550776446</v>
+        <v>762.69927314158656</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
@@ -2147,7 +2147,7 @@
         <v>113</v>
       </c>
       <c r="C111">
-        <v>790.00713698612094</v>
+        <v>719.51850718712819</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
@@ -2155,7 +2155,7 @@
         <v>112</v>
       </c>
       <c r="C112">
-        <v>789.99362238663866</v>
+        <v>719.29590006004116</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -2163,7 +2163,7 @@
         <v>118</v>
       </c>
       <c r="C113">
-        <v>721.92770848403484</v>
+        <v>714.65126294214508</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -2171,7 +2171,7 @@
         <v>115</v>
       </c>
       <c r="C114">
-        <v>721.6188793057969</v>
+        <v>712.89419233216563</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -2179,7 +2179,7 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>721.19489348482614</v>
+        <v>709.90471019240908</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -2187,7 +2187,7 @@
         <v>116</v>
       </c>
       <c r="C116">
-        <v>713.68353974293655</v>
+        <v>708.56126313973755</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -2195,7 +2195,7 @@
         <v>117</v>
       </c>
       <c r="C117">
-        <v>713.62247182633575</v>
+        <v>708.29200707578957</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -2203,7 +2203,7 @@
         <v>119</v>
       </c>
       <c r="C118">
-        <v>713.50033599313429</v>
+        <v>704.5224114941783</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -2211,7 +2211,7 @@
         <v>120</v>
       </c>
       <c r="C119">
-        <v>708.00422349906876</v>
+        <v>697.53800962367177</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -2219,7 +2219,7 @@
         <v>121</v>
       </c>
       <c r="C120">
-        <v>702.52183271986041</v>
+        <v>693.37280426048653</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -2227,7 +2227,7 @@
         <v>122</v>
       </c>
       <c r="C121">
-        <v>701.09315895809743</v>
+        <v>692.50438341053359</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -2235,7 +2235,7 @@
         <v>123</v>
       </c>
       <c r="C122">
-        <v>694.28995056875033</v>
+        <v>691.40998990167702</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -2243,7 +2243,7 @@
         <v>124</v>
       </c>
       <c r="C123">
-        <v>909.44307380517637</v>
+        <v>909.44307380517671</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -2251,7 +2251,7 @@
         <v>125</v>
       </c>
       <c r="C124">
-        <v>904.1683906914476</v>
+        <v>903.11149526314784</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -2259,7 +2259,7 @@
         <v>126</v>
       </c>
       <c r="C125">
-        <v>887.6022177417658</v>
+        <v>872.2296189059773</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -2267,7 +2267,7 @@
         <v>127</v>
       </c>
       <c r="C126">
-        <v>845.81565588042497</v>
+        <v>834.04281032292079</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
